--- a/artfynd/A 58584-2021 artfynd.xlsx
+++ b/artfynd/A 58584-2021 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125256832</v>
+        <v>125256839</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>79926</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564223</v>
+        <v>564094</v>
       </c>
       <c r="R3" t="n">
-        <v>6983362</v>
+        <v>6983394</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125256839</v>
+        <v>125256832</v>
       </c>
       <c r="B4" t="n">
-        <v>79926</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,20 +904,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564094</v>
+        <v>564223</v>
       </c>
       <c r="R4" t="n">
-        <v>6983394</v>
+        <v>6983362</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 58584-2021 artfynd.xlsx
+++ b/artfynd/A 58584-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125256846</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>125256839</v>
       </c>
       <c r="B3" t="n">
-        <v>79926</v>
+        <v>80063</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>125256832</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 58584-2021 artfynd.xlsx
+++ b/artfynd/A 58584-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125256846</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,32 +781,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125256839</v>
+        <v>125256832</v>
       </c>
       <c r="B3" t="n">
-        <v>80063</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564094</v>
+        <v>564223</v>
       </c>
       <c r="R3" t="n">
-        <v>6983394</v>
+        <v>6983362</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,32 +882,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125256832</v>
+        <v>125256839</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564223</v>
+        <v>564094</v>
       </c>
       <c r="R4" t="n">
-        <v>6983362</v>
+        <v>6983394</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 58584-2021 artfynd.xlsx
+++ b/artfynd/A 58584-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125256846</v>
       </c>
       <c r="B2" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>125256832</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>125256839</v>
       </c>
       <c r="B4" t="n">
-        <v>80105</v>
+        <v>80106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 58584-2021 artfynd.xlsx
+++ b/artfynd/A 58584-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125256846</v>
+        <v>125256843</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563317</v>
+        <v>563770</v>
       </c>
       <c r="R2" t="n">
-        <v>6983730</v>
+        <v>6983837</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>på mycket gammal sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125256832</v>
+        <v>125256846</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564223</v>
+        <v>563317</v>
       </c>
       <c r="R3" t="n">
-        <v>6983362</v>
+        <v>6983730</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,6 +847,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>på mycket gammal sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125256839</v>
+        <v>125256837</v>
       </c>
       <c r="B4" t="n">
-        <v>80106</v>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -893,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564094</v>
+        <v>564020</v>
       </c>
       <c r="R4" t="n">
-        <v>6983394</v>
+        <v>6983482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,6 +976,314 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>125256832</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högklippen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>564223</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6983362</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125256825</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Högklippen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>564419</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6983397</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på döende sälg</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125256839</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Högklippen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>564094</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6983394</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Thomas Stålhandske</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>

--- a/artfynd/A 58584-2021 artfynd.xlsx
+++ b/artfynd/A 58584-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125256843</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125256846</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125256837</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125256832</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125256825</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,8 +1318,21 @@
           <t>LstZ naturskyddsfunktionens naturvärdesinventering 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125256839</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>